--- a/GEMAS.xlsx
+++ b/GEMAS.xlsx
@@ -593,52 +593,52 @@
     <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,6 +655,291 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="25">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -730,155 +1015,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2E4057"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
@@ -1151,202 +1287,7 @@
           <bgColor rgb="FFF0F4F8"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Century Gothic"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0F4F8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
@@ -1479,22 +1420,81 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
         <bottom style="thin">
           <color rgb="FFCCCCCC"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0F4F8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Century Gothic"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2E4057"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
-        <top style="thin">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1511,32 +1511,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B150012-F422-4681-B417-9B76375E8139}" name="Tabla1" displayName="Tabla1" ref="A1:U14" totalsRowShown="0" headerRowDxfId="3" dataDxfId="5" headerRowBorderDxfId="23" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B150012-F422-4681-B417-9B76375E8139}" name="Tabla1" displayName="Tabla1" ref="A1:U14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21">
   <autoFilter ref="A1:U14" xr:uid="{9B150012-F422-4681-B417-9B76375E8139}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{2BB1E1FA-FB41-40AD-8901-3DD6E572AAF8}" name="SKU" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{A3DD64BB-2E35-4833-8BF4-F6E2EB119882}" name="Gema" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{C43BE31B-D136-4631-806E-ACC5C9805FCA}" name="Peso (ct)" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{7FE2189A-C009-4E84-A5DC-ECAB70F06534}" name="Dimensiones (mm)" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{3A80D51F-1A23-44C9-9D7E-41A0067CB1F7}" name="Certificado" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{8A91EAE2-E750-491A-8A24-ABA5174A1FD3}" name="Color" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{2D3D7685-EA02-40E0-8E96-7E2DCBB88D15}" name="Tratamiento" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{3E8AC997-7DD5-452C-840F-9DAB4803FF36}" name="Sellado" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{405A8E6A-A346-4E3B-8FFD-EC9FA3E8C9F9}" name="Forma" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{67BE6327-D242-45AE-9FA1-1B5C8989B84C}" name="Pureza" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{83A8A03D-7578-457F-BB44-FBE28C2CB19F}" name="Origen" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{DEBBA08A-174E-4A70-87CE-50B5DA7AE3C4}" name="Notas" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{8B7BFA4C-D8FA-4B33-B786-6E5EB74694F2}" name="Fecha de compra" dataDxfId="0"/>
-    <tableColumn id="14" xr3:uid="{2C553D06-60B2-409F-9F14-00CB663D235F}" name="Vendedor" dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{DF34C1B6-DB4A-4900-8D15-31E1BE5BDC79}" name="Precio" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{2E05AF3B-1F70-499B-BA4D-DB9321206C07}" name="Portes" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{645F20AE-5784-4F5C-9728-1228FB4FF3F0}" name="Total" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{2BB1E1FA-FB41-40AD-8901-3DD6E572AAF8}" name="SKU" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{A3DD64BB-2E35-4833-8BF4-F6E2EB119882}" name="Gema" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{C43BE31B-D136-4631-806E-ACC5C9805FCA}" name="Peso (ct)" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{7FE2189A-C009-4E84-A5DC-ECAB70F06534}" name="Dimensiones (mm)" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{3A80D51F-1A23-44C9-9D7E-41A0067CB1F7}" name="Certificado" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{8A91EAE2-E750-491A-8A24-ABA5174A1FD3}" name="Color" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{2D3D7685-EA02-40E0-8E96-7E2DCBB88D15}" name="Tratamiento" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{3E8AC997-7DD5-452C-840F-9DAB4803FF36}" name="Sellado" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{405A8E6A-A346-4E3B-8FFD-EC9FA3E8C9F9}" name="Forma" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{67BE6327-D242-45AE-9FA1-1B5C8989B84C}" name="Pureza" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{83A8A03D-7578-457F-BB44-FBE28C2CB19F}" name="Origen" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{DEBBA08A-174E-4A70-87CE-50B5DA7AE3C4}" name="Notas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{8B7BFA4C-D8FA-4B33-B786-6E5EB74694F2}" name="Fecha de compra" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{2C553D06-60B2-409F-9F14-00CB663D235F}" name="Vendedor" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{DF34C1B6-DB4A-4900-8D15-31E1BE5BDC79}" name="Precio" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{2E05AF3B-1F70-499B-BA4D-DB9321206C07}" name="Portes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{645F20AE-5784-4F5C-9728-1228FB4FF3F0}" name="Total" dataDxfId="4">
       <calculatedColumnFormula>SUM(O2:P2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{9BF619C7-36FE-45E5-BF05-AEF92A06CAAE}" name="Rango mín." dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{DEAE31A4-F8FD-420D-AEDF-DAE310C413A1}" name="Rango máx." dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{C2AC92DD-8E6E-432D-91C4-BF0E65B3CDA3}" name="Ubicación" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{B82C1AD2-61D2-4502-B95D-6C9C115A7A34}" name="Anotaciones" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{9BF619C7-36FE-45E5-BF05-AEF92A06CAAE}" name="Rango mín." dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{DEAE31A4-F8FD-420D-AEDF-DAE310C413A1}" name="Rango máx." dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{C2AC92DD-8E6E-432D-91C4-BF0E65B3CDA3}" name="Ubicación" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{B82C1AD2-61D2-4502-B95D-6C9C115A7A34}" name="Anotaciones" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/GEMAS.xlsx
+++ b/GEMAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\coleccion-gemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE6947F-C85B-443C-8F37-D96C433038BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABF70C3-839A-4871-93D7-44F4602F4A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="130">
   <si>
     <t>SKU</t>
   </si>
@@ -278,9 +278,6 @@
     <t xml:space="preserve">Octogonal </t>
   </si>
   <si>
-    <t>Sin fluorescencia</t>
-  </si>
-  <si>
     <t>ALGT-92444619</t>
   </si>
   <si>
@@ -423,6 +420,12 @@
   </si>
   <si>
     <t>Comprada en Tailandia. Ebn portes se incluyen 21 € de IVA</t>
+  </si>
+  <si>
+    <t>Sin fluorescencia - Tasación IGE: 450,00 €; Pureza: moderadas inclusiones</t>
+  </si>
+  <si>
+    <t>Transparente; Espodumena natural</t>
   </si>
 </sst>
 </file>
@@ -1833,7 +1836,7 @@
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="14.44140625" customWidth="1"/>
@@ -1949,7 +1952,7 @@
         <v>24</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O2" s="8">
         <v>280</v>
@@ -2017,7 +2020,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O3" s="11">
         <v>53</v>
@@ -2235,7 +2238,7 @@
         <v>50</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -2253,35 +2256,35 @@
         <v>30.76</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>45</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>35</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O7" s="11">
         <v>107</v>
@@ -2303,7 +2306,7 @@
         <v>50</v>
       </c>
       <c r="U7" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
@@ -2321,35 +2324,35 @@
         <v>1.84</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="G8" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>37</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O8" s="8">
         <v>52</v>
@@ -2387,13 +2390,13 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="D9" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>56</v>
@@ -2402,18 +2405,18 @@
         <v>45</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O9" s="11">
         <v>107</v>
@@ -2451,25 +2454,25 @@
         <v>84.16</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -2477,7 +2480,7 @@
         <v>40</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O10" s="8">
         <v>101</v>
@@ -2515,33 +2518,33 @@
         <v>45.57</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O11" s="11">
         <v>71</v>
@@ -2582,7 +2585,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>43</v>
@@ -2603,13 +2606,13 @@
         <v>48</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>49</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O12" s="8">
         <v>85</v>
@@ -2631,7 +2634,7 @@
         <v>50</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
@@ -2643,19 +2646,19 @@
         <v>712</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="13">
         <v>4.7</v>
       </c>
       <c r="D13" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>119</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>120</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>56</v>
@@ -2664,10 +2667,10 @@
         <v>45</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
@@ -2675,7 +2678,7 @@
         <v>46132</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O13" s="13">
         <v>52</v>
@@ -2707,19 +2710,19 @@
         <v>713</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="15">
         <v>26.57</v>
       </c>
       <c r="D14" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="F14" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>125</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
@@ -2732,16 +2735,16 @@
         <v>47</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M14" s="22">
         <v>46153</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O14" s="15">
         <v>75</v>
@@ -2760,10 +2763,10 @@
         <v>1400</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
